--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
+          <t>If FASTQ, BAM, or CRAM files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
+          <t>If FASTQ files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>If FASTQ files, are the reads paired end?</t>
+          <t>If FASTQ files, are the reads paired end? Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$20</formula1>
+      <formula1>'Lists'!$C$2:$C$21</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -3005,6 +3005,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Extracellular Vesicles</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$21</formula1>
+      <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -3005,11 +3005,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Extracellular Vesicles</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>
